--- a/config/standards/TPF_Operator_Standards.xlsx
+++ b/config/standards/TPF_Operator_Standards.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,10 +531,18 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>2026-10-02 (standards rebuild, tpf-app mirror): US Police PFT run / push-ups / sit-ups now come from US military score tables (US Navy PRT 1.5-mile; USAF PFRA 1-min charts) — they were stated as Cooper Institute LE standards, which TPF has no permission to use. Navy SEAL 500 m swim: the PST swim is 500 yards, so its times are converted to 500 m (x 1.0995); Royal Marines' derived swim follows. The raw matrix (TPF_ORS_Standards_2026-05-21.xlsx) still carries the old Cooper-cited police rows — do not rebuild this master from it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-02, later (Navy PRT + the minimum / good / maximum rule, tpf-app mirror): a ladder read off a general military table puts the official maximum at Excellent at most, with Elite above it (TPF's margin: +10 % reps / hold, -5 % time) — USMC and US Police PFT Elites moved; SEAL pull-up Pass raised to the PST minimum (10). New unit 'US Navy (PRT)' on the Navy PRT Guide-5 (Jan 2025) table, men 17-19. Two new columns: 'id' (overrides the id codegen makes from the name; blank = as before) and 'alternative_group' (benchmarks sharing one score once, at the best — the Navy cardio event). Record: scripts/apply-navy-prt-and-military-tiers-2026-10-02.py.</t>
         </is>
       </c>
     </row>
@@ -549,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L179"/>
+  <dimension ref="A1:N192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,6 +628,16 @@
           <t>source</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>alternative_group</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -669,12 +687,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 18:00 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -915,11 +933,11 @@
         <v>18</v>
       </c>
       <c r="J8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 23 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -964,11 +982,11 @@
         <v>75</v>
       </c>
       <c r="J9" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 87 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1038,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3:45</t>
+          <t>4:10</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 3:45 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3485,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H57" t="n">
         <v>13</v>
@@ -3480,7 +3498,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Pass = the BUD/S PST minimum of 10 (was 8, below it) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5239,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5246,27 +5264,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>9:45</t>
+          <t>9:15</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>8:30</t>
+          <t>7:50</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>US Navy PRT 1.5-mile, men 20-24 (Guide-5, Jan 2025, a US government work) — tpf-app mirror 2026-10-02</t>
+          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>prt_cardio</t>
         </is>
       </c>
     </row>
@@ -5278,44 +5301,62 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>running</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Back Squat</t>
+          <t>2 km row (alternate)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
-        <v>80</v>
-      </c>
-      <c r="H92" t="n">
-        <v>100</v>
-      </c>
-      <c r="I92" t="n">
-        <v>120</v>
-      </c>
-      <c r="J92" t="n">
-        <v>140</v>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>9:20</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>8:10</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>7:30</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>6:40</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>row_2k</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>prt_cardio</t>
         </is>
       </c>
     </row>
@@ -5327,44 +5368,57 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>running</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Hex-bar DL</t>
+          <t>500-yd swim (alternate)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
-        <v>100</v>
-      </c>
-      <c r="H93" t="n">
-        <v>125</v>
-      </c>
-      <c r="I93" t="n">
-        <v>150</v>
-      </c>
-      <c r="J93" t="n">
-        <v>170</v>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>9:15</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>7:45</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>6:10</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>prt_cardio</t>
         </is>
       </c>
     </row>
@@ -5376,44 +5430,57 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>running</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Conventional DL</t>
+          <t>450 m swim (alternate)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>90</v>
-      </c>
-      <c r="H94" t="n">
-        <v>115</v>
-      </c>
-      <c r="I94" t="n">
-        <v>140</v>
-      </c>
-      <c r="J94" t="n">
-        <v>160</v>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>9:05</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>7:35</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>6:00</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>prt_cardio</t>
         </is>
       </c>
     </row>
@@ -5425,17 +5492,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>upper_strength</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Back Squat</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5449,20 +5516,20 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H95" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="I95" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="J95" t="n">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5474,22 +5541,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Pull-ups (no time)</t>
+          <t>Hex-bar DL</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5498,20 +5565,20 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="H96" t="n">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="I96" t="n">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="J96" t="n">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5523,22 +5590,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Push-ups (1 min)</t>
+          <t>Conventional DL</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5547,20 +5614,20 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H97" t="n">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="I97" t="n">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="J97" t="n">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>USAF PFRA 1-min push-ups, men under 25 (eff. 1 Mar 2026, a US government work) — tpf-app mirror 2026-10-02</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5572,22 +5639,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>core_endurance</t>
+          <t>upper_strength</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sit-ups (1 min)</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5596,20 +5663,20 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="H98" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="I98" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="J98" t="n">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>USAF PFRA 1-min sit-ups, men under 25 (eff. 1 Mar 2026, a US government work) — tpf-app mirror 2026-10-02</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5621,22 +5688,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>upper_endurance</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Plank (front)</t>
+          <t>Push-ups (2 min)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>reps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5644,29 +5711,21 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>1:00</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>1:30</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2:30</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>3:30</t>
-        </is>
+      <c r="G99" t="n">
+        <v>42</v>
+      </c>
+      <c r="H99" t="n">
+        <v>68</v>
+      </c>
+      <c r="I99" t="n">
+        <v>82</v>
+      </c>
+      <c r="J99" t="n">
+        <v>101</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5737,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5688,7 +5747,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Side plank (per side)</t>
+          <t>Forearm plank</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5703,27 +5762,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>0:45</t>
+          <t>1:11</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1:00</t>
+          <t>2:23</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1:30</t>
+          <t>3:04</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2:00</t>
+          <t>3:45</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>plank_front</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5799,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5745,7 +5809,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Dead hang</t>
+          <t>Dead hang (grip)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5780,7 +5844,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5856,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5816,20 +5880,20 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H102" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I102" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J102" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5905,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>US Police PFT</t>
+          <t>US Navy (PRT)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5878,7 +5942,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5954,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5915,27 +5979,27 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>9:00</t>
+          <t>9:45</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>8:30</t>
+          <t>8:05</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>US Navy PRT 1.5-mile, men 20-24 (Guide-5, Jan 2025, a US government work); Elite above Outstanding High 8:30 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5947,7 +6011,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5971,16 +6035,16 @@
         </is>
       </c>
       <c r="G105" t="n">
+        <v>80</v>
+      </c>
+      <c r="H105" t="n">
         <v>100</v>
       </c>
-      <c r="H105" t="n">
-        <v>125</v>
-      </c>
       <c r="I105" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="J105" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5996,7 +6060,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6020,16 +6084,16 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H106" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="I106" t="n">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="J106" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -6045,7 +6109,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6069,16 +6133,16 @@
         </is>
       </c>
       <c r="G107" t="n">
+        <v>90</v>
+      </c>
+      <c r="H107" t="n">
         <v>115</v>
       </c>
-      <c r="H107" t="n">
-        <v>145</v>
-      </c>
       <c r="I107" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="J107" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6094,7 +6158,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6118,16 +6182,16 @@
         </is>
       </c>
       <c r="G108" t="n">
+        <v>65</v>
+      </c>
+      <c r="H108" t="n">
         <v>80</v>
       </c>
-      <c r="H108" t="n">
-        <v>100</v>
-      </c>
       <c r="I108" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="J108" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6143,22 +6207,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>upper_strength</t>
+          <t>upper_endurance</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Pull-ups (no time)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>reps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6167,16 +6231,16 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H109" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="I109" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="J109" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6192,7 +6256,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6202,7 +6266,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Pull-ups (no time)</t>
+          <t>Push-ups (1 min)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6216,20 +6280,20 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H110" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="I110" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="J110" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>USAF PFRA 1-min push-ups, men under 25 (eff. 1 Mar 2026, a US government work); Elite above the maximum 67 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -6241,17 +6305,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>core_endurance</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Push-ups (1 min)</t>
+          <t>Sit-ups (1 min)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6265,20 +6329,20 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H111" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="I111" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="J111" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>USAF PFRA 1-min sit-ups, men under 25 (eff. 1 Mar 2026, a US government work); Elite above the maximum 58 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -6290,22 +6354,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>core_endurance</t>
+          <t>stability</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sit-ups (2 min)</t>
+          <t>Plank (front)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6313,17 +6377,25 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>40</v>
-      </c>
-      <c r="H112" t="n">
-        <v>55</v>
-      </c>
-      <c r="I112" t="n">
-        <v>70</v>
-      </c>
-      <c r="J112" t="n">
-        <v>90</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1:00</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2:30</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6339,7 +6411,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6349,7 +6421,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Plank (front)</t>
+          <t>Side plank (per side)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6364,22 +6436,22 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
+          <t>0:45</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>1:00</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
           <t>1:30</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>2:30</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>3:30</t>
-        </is>
-      </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>4:30</t>
+          <t>2:00</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6396,17 +6468,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>grip</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Side plank (per side)</t>
+          <t>Dead hang</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6421,22 +6493,22 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1:00</t>
+          <t>0:30</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1:30</t>
+          <t>0:50</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2:00</t>
+          <t>1:15</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>3:00</t>
+          <t>1:40</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6453,22 +6525,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>grip</t>
+          <t>power</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Dead hang</t>
+          <t>Power Clean</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6476,25 +6548,17 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>0:45</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1:15</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1:40</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>2:10</t>
-        </is>
+      <c r="G115" t="n">
+        <v>45</v>
+      </c>
+      <c r="H115" t="n">
+        <v>60</v>
+      </c>
+      <c r="I115" t="n">
+        <v>75</v>
+      </c>
+      <c r="J115" t="n">
+        <v>90</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6510,7 +6574,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>US SWAT</t>
+          <t>US Police PFT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6520,12 +6584,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Power Clean</t>
+          <t>Broad Jump</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6534,16 +6598,16 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>65</v>
+        <v>1.7</v>
       </c>
       <c r="H116" t="n">
-        <v>85</v>
+        <v>1.9</v>
       </c>
       <c r="I116" t="n">
-        <v>100</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
-        <v>120</v>
+        <v>2.3</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6564,35 +6628,43 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>running</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Broad Jump</t>
+          <t>1.5-mile run</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H117" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I117" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J117" t="n">
-        <v>2.5</v>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>9:00</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>8:30</t>
+        </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6603,53 +6675,45 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2 km run (best effort)</t>
+          <t>Back Squat</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>lower-is-better</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>8:15</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>7:45</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>7:15</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>6:45</t>
-        </is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>100</v>
+      </c>
+      <c r="H118" t="n">
+        <v>125</v>
+      </c>
+      <c r="I118" t="n">
+        <v>150</v>
+      </c>
+      <c r="J118" t="n">
+        <v>175</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6660,53 +6724,45 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>rucking</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10-mile ruck</t>
+          <t>Hex-bar DL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>lower-is-better</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>2:00:00</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>1:50:00</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1:42:00</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>1:35:00</t>
-        </is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>130</v>
+      </c>
+      <c r="H119" t="n">
+        <v>160</v>
+      </c>
+      <c r="I119" t="n">
+        <v>185</v>
+      </c>
+      <c r="J119" t="n">
+        <v>210</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6717,12 +6773,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6732,7 +6788,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Back Squat</t>
+          <t>Conventional DL</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6746,16 +6802,16 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H120" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="I120" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="J120" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6766,22 +6822,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>upper_strength</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Hex-bar DL</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6795,16 +6851,16 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="H121" t="n">
+        <v>100</v>
+      </c>
+      <c r="I121" t="n">
+        <v>120</v>
+      </c>
+      <c r="J121" t="n">
         <v>140</v>
-      </c>
-      <c r="I121" t="n">
-        <v>180</v>
-      </c>
-      <c r="J121" t="n">
-        <v>200</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6815,22 +6871,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>upper_strength</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Conventional DL</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6844,16 +6900,16 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="H122" t="n">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="I122" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="J122" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6864,27 +6920,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>upper_strength</t>
+          <t>upper_endurance</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Pull-ups (no time)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>reps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6893,16 +6949,16 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="H123" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="I123" t="n">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="J123" t="n">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6913,12 +6969,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6928,7 +6984,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Pull-ups (no time)</t>
+          <t>Push-ups (1 min)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6942,16 +6998,16 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H124" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="I124" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="J124" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6962,22 +7018,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>core_endurance</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Push-ups (2 min)</t>
+          <t>Sit-ups (2 min)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6991,16 +7047,16 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H125" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I125" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J125" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -7011,27 +7067,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>core_endurance</t>
+          <t>stability</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sit-ups (2 min)</t>
+          <t>Plank (front)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7039,17 +7095,25 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>30</v>
-      </c>
-      <c r="H126" t="n">
-        <v>50</v>
-      </c>
-      <c r="I126" t="n">
-        <v>65</v>
-      </c>
-      <c r="J126" t="n">
-        <v>80</v>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2:30</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>4:30</t>
+        </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -7060,12 +7124,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7075,7 +7139,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Plank (front)</t>
+          <t>Side plank (per side)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7090,22 +7154,22 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
+          <t>1:00</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
           <t>1:30</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>2:30</t>
-        </is>
-      </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3:30</t>
+          <t>2:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>4:30</t>
+          <t>3:00</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -7117,22 +7181,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>grip</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Side plank (per side)</t>
+          <t>Dead hang</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7147,22 +7211,22 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>1:00</t>
+          <t>0:45</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1:30</t>
+          <t>1:15</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2:00</t>
+          <t>1:40</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>3:00</t>
+          <t>2:10</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -7174,27 +7238,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>grip</t>
+          <t>power</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Dead hang (grip)</t>
+          <t>Power Clean</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7202,25 +7266,17 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>0:30</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1:00</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1:30</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>2:00</t>
-        </is>
+      <c r="G129" t="n">
+        <v>65</v>
+      </c>
+      <c r="H129" t="n">
+        <v>85</v>
+      </c>
+      <c r="I129" t="n">
+        <v>100</v>
+      </c>
+      <c r="J129" t="n">
+        <v>120</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7231,12 +7287,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>UK Parachute Regiment (P Coy)</t>
+          <t>US SWAT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7246,12 +7302,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Power Clean</t>
+          <t>Broad Jump</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7260,16 +7316,16 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>55</v>
+        <v>1.9</v>
       </c>
       <c r="H130" t="n">
-        <v>75</v>
+        <v>2.1</v>
       </c>
       <c r="I130" t="n">
-        <v>90</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
-        <v>110</v>
+        <v>2.5</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7290,35 +7346,43 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>running</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Broad Jump</t>
+          <t>2 km run (best effort)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H131" t="n">
-        <v>2</v>
-      </c>
-      <c r="I131" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J131" t="n">
-        <v>2.4</v>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>8:15</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>7:45</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>7:15</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>6:45</t>
+        </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7334,17 +7398,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>rucking</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>1.5-mile run</t>
+          <t>10-mile ruck</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7359,22 +7423,22 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>2:00:00</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>9:30</t>
+          <t>1:50:00</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>9:00</t>
+          <t>1:42:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>8:30</t>
+          <t>1:35:00</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -7391,48 +7455,40 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>rucking</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>10-mile ruck</t>
+          <t>Back Squat</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>lower-is-better</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>2:06:00</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>1:55:30</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1:47:06</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>1:39:45</t>
-        </is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>100</v>
+      </c>
+      <c r="H133" t="n">
+        <v>120</v>
+      </c>
+      <c r="I133" t="n">
+        <v>140</v>
+      </c>
+      <c r="J133" t="n">
+        <v>160</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7448,52 +7504,44 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>500 m swim</t>
+          <t>Hex-bar DL</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>lower-is-better</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>110</v>
+      </c>
+      <c r="H134" t="n">
+        <v>140</v>
+      </c>
+      <c r="I134" t="n">
+        <v>180</v>
+      </c>
+      <c r="J134" t="n">
+        <v>200</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Derived: SEAL PST swim (converted to 500 m) x 1.15 — tpf-app mirror 2026-10-02</t>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7553,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7515,7 +7563,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Back Squat</t>
+          <t>Conventional DL</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7529,13 +7577,13 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H135" t="n">
         <v>135</v>
       </c>
       <c r="I135" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="J135" t="n">
         <v>180</v>
@@ -7554,17 +7602,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>upper_strength</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Hex-bar DL</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7578,16 +7626,16 @@
         </is>
       </c>
       <c r="G136" t="n">
+        <v>75</v>
+      </c>
+      <c r="H136" t="n">
+        <v>90</v>
+      </c>
+      <c r="I136" t="n">
+        <v>110</v>
+      </c>
+      <c r="J136" t="n">
         <v>130</v>
-      </c>
-      <c r="H136" t="n">
-        <v>160</v>
-      </c>
-      <c r="I136" t="n">
-        <v>190</v>
-      </c>
-      <c r="J136" t="n">
-        <v>215</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7603,22 +7651,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>upper_endurance</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Conventional DL</t>
+          <t>Pull-ups (no time)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>reps</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7627,16 +7675,16 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="H137" t="n">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="I137" t="n">
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="J137" t="n">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7652,22 +7700,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>upper_strength</t>
+          <t>upper_endurance</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Push-ups (2 min)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>reps</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7676,16 +7724,16 @@
         </is>
       </c>
       <c r="G138" t="n">
+        <v>25</v>
+      </c>
+      <c r="H138" t="n">
+        <v>40</v>
+      </c>
+      <c r="I138" t="n">
+        <v>60</v>
+      </c>
+      <c r="J138" t="n">
         <v>80</v>
-      </c>
-      <c r="H138" t="n">
-        <v>100</v>
-      </c>
-      <c r="I138" t="n">
-        <v>120</v>
-      </c>
-      <c r="J138" t="n">
-        <v>140</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7701,17 +7749,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>core_endurance</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Pull-ups (no time)</t>
+          <t>Sit-ups (2 min)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7725,16 +7773,16 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H139" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I139" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="J139" t="n">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7750,22 +7798,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>stability</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Push-ups (2 min)</t>
+          <t>Plank (front)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7773,17 +7821,25 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>50</v>
-      </c>
-      <c r="H140" t="n">
-        <v>65</v>
-      </c>
-      <c r="I140" t="n">
-        <v>80</v>
-      </c>
-      <c r="J140" t="n">
-        <v>100</v>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2:30</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>4:30</t>
+        </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7799,22 +7855,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>core_endurance</t>
+          <t>stability</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sit-ups (2 min)</t>
+          <t>Side plank (per side)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7822,17 +7878,25 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G141" t="n">
-        <v>50</v>
-      </c>
-      <c r="H141" t="n">
-        <v>75</v>
-      </c>
-      <c r="I141" t="n">
-        <v>90</v>
-      </c>
-      <c r="J141" t="n">
-        <v>110</v>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>1:00</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2:00</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>3:00</t>
+        </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7848,17 +7912,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>grip</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Plank (front)</t>
+          <t>Dead hang (grip)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7873,22 +7937,22 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
+          <t>0:30</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1:00</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
           <t>1:30</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>2:30</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>3:30</t>
-        </is>
-      </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>4:30</t>
+          <t>2:00</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -7905,22 +7969,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>power</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Side plank (per side)</t>
+          <t>Power Clean</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7928,25 +7992,17 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>1:00</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>1:30</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2:00</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>3:00</t>
-        </is>
+      <c r="G143" t="n">
+        <v>55</v>
+      </c>
+      <c r="H143" t="n">
+        <v>75</v>
+      </c>
+      <c r="I143" t="n">
+        <v>90</v>
+      </c>
+      <c r="J143" t="n">
+        <v>110</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7962,22 +8018,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>UK Royal Marines (Cdo Course)</t>
+          <t>UK Parachute Regiment (P Coy)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>grip</t>
+          <t>power</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Dead hang (grip)</t>
+          <t>Broad Jump</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7985,25 +8041,17 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>0:45</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>1:15</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1:50</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>2:30</t>
-        </is>
+      <c r="G144" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H144" t="n">
+        <v>2</v>
+      </c>
+      <c r="I144" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J144" t="n">
+        <v>2.4</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -8024,35 +8072,43 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>running</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Power Clean</t>
+          <t>1.5-mile run</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G145" t="n">
-        <v>65</v>
-      </c>
-      <c r="H145" t="n">
-        <v>85</v>
-      </c>
-      <c r="I145" t="n">
-        <v>100</v>
-      </c>
-      <c r="J145" t="n">
-        <v>120</v>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>9:30</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>9:00</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>8:30</t>
+        </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -8073,35 +8129,43 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>rucking</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Broad Jump</t>
+          <t>10-mile ruck</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G146" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H146" t="n">
-        <v>2</v>
-      </c>
-      <c r="I146" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J146" t="n">
-        <v>2.4</v>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2:06:00</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>1:55:30</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1:47:06</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>1:39:45</t>
+        </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8117,17 +8181,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2 km run (best effort)</t>
+          <t>500 m swim</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8142,27 +8206,27 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>8:42</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>7:52</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>7:27</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>6:39</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>Derived: SEAL PST swim (converted to 500 m) x 1.15 — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -8174,48 +8238,40 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>rucking</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>5-mile ruck (30 kg)</t>
+          <t>Back Squat</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>lower-is-better</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>1:15:00</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>1:10:00</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1:05:00</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>1:00:00</t>
-        </is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>100</v>
+      </c>
+      <c r="H148" t="n">
+        <v>135</v>
+      </c>
+      <c r="I148" t="n">
+        <v>150</v>
+      </c>
+      <c r="J148" t="n">
+        <v>180</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -8231,48 +8287,40 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>rucking</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Fan Dance (24 km @ 35 lb + rifle) — optional</t>
+          <t>Hex-bar DL</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>lower-is-better</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>4:00:00</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>3:30:00</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>3:15:00</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>3:00:00</t>
-        </is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>130</v>
+      </c>
+      <c r="H149" t="n">
+        <v>160</v>
+      </c>
+      <c r="I149" t="n">
+        <v>190</v>
+      </c>
+      <c r="J149" t="n">
+        <v>215</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -8288,7 +8336,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8298,7 +8346,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Back Squat</t>
+          <t>Conventional DL</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8312,16 +8360,16 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H150" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="I150" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="J150" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -8337,17 +8385,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>upper_strength</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Hex-bar DL</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8361,16 +8409,16 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="H151" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="I151" t="n">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="J151" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -8386,22 +8434,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>upper_endurance</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Conventional DL</t>
+          <t>Pull-ups (no time)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>reps</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8410,16 +8458,16 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>115</v>
+        <v>8</v>
       </c>
       <c r="H152" t="n">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="I152" t="n">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="J152" t="n">
-        <v>185</v>
+        <v>22</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -8435,22 +8483,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>upper_strength</t>
+          <t>upper_endurance</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Push-ups (2 min)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>reps</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8459,16 +8507,16 @@
         </is>
       </c>
       <c r="G153" t="n">
+        <v>50</v>
+      </c>
+      <c r="H153" t="n">
+        <v>65</v>
+      </c>
+      <c r="I153" t="n">
         <v>80</v>
       </c>
-      <c r="H153" t="n">
-        <v>95</v>
-      </c>
-      <c r="I153" t="n">
-        <v>110</v>
-      </c>
       <c r="J153" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -8484,17 +8532,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>core_endurance</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Pull-ups (no time)</t>
+          <t>Sit-ups (2 min)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8508,16 +8556,16 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="H154" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="I154" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J154" t="n">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -8533,22 +8581,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>stability</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Push-ups (2 min)</t>
+          <t>Plank (front)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8556,17 +8604,25 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G155" t="n">
-        <v>50</v>
-      </c>
-      <c r="H155" t="n">
-        <v>65</v>
-      </c>
-      <c r="I155" t="n">
-        <v>80</v>
-      </c>
-      <c r="J155" t="n">
-        <v>100</v>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2:30</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>4:30</t>
+        </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -8582,22 +8638,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>core_endurance</t>
+          <t>stability</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Sit-ups (2 min)</t>
+          <t>Side plank (per side)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8605,17 +8661,25 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G156" t="n">
-        <v>50</v>
-      </c>
-      <c r="H156" t="n">
-        <v>75</v>
-      </c>
-      <c r="I156" t="n">
-        <v>90</v>
-      </c>
-      <c r="J156" t="n">
-        <v>110</v>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>1:00</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2:00</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>3:00</t>
+        </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -8631,17 +8695,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>grip</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Plank (front)</t>
+          <t>Dead hang (grip)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8656,22 +8720,22 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>1:30</t>
+          <t>0:45</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
+          <t>1:15</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
           <t>2:30</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>3:30</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>4:30</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -8688,22 +8752,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>power</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Side plank (per side)</t>
+          <t>Power Clean</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -8711,25 +8775,17 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>1:00</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>1:30</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2:00</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>3:00</t>
-        </is>
+      <c r="G158" t="n">
+        <v>65</v>
+      </c>
+      <c r="H158" t="n">
+        <v>85</v>
+      </c>
+      <c r="I158" t="n">
+        <v>100</v>
+      </c>
+      <c r="J158" t="n">
+        <v>120</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8745,22 +8801,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>UK Special Forces (SAS/SBS)</t>
+          <t>UK Royal Marines (Cdo Course)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>grip</t>
+          <t>power</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Dead hang (grip)</t>
+          <t>Broad Jump</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8768,25 +8824,17 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>0:45</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>1:15</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1:50</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>2:30</t>
-        </is>
+      <c r="G159" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H159" t="n">
+        <v>2</v>
+      </c>
+      <c r="I159" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J159" t="n">
+        <v>2.4</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -8802,7 +8850,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8827,22 +8875,22 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>8:42</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>8:45</t>
+          <t>7:52</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>7:45</t>
+          <t>7:27</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>7:15</t>
+          <t>6:39</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -8859,7 +8907,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8869,7 +8917,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>8-mile loaded march (25 kg)</t>
+          <t>5-mile ruck (30 kg)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8884,22 +8932,22 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2:00:00</t>
+          <t>1:15:00</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>1:55:00</t>
+          <t>1:10:00</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>1:50:00</t>
+          <t>1:05:00</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>1:40:00</t>
+          <t>1:00:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -8916,40 +8964,48 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>lower_strength</t>
+          <t>rucking</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Back Squat</t>
+          <t>Fan Dance (24 km @ 35 lb + rifle) — optional</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G162" t="n">
-        <v>100</v>
-      </c>
-      <c r="H162" t="n">
-        <v>130</v>
-      </c>
-      <c r="I162" t="n">
-        <v>155</v>
-      </c>
-      <c r="J162" t="n">
-        <v>175</v>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>4:00:00</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>3:30:00</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>3:15:00</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>3:00:00</t>
+        </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -8965,7 +9021,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8975,7 +9031,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Hex-bar DL</t>
+          <t>Back Squat</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8989,16 +9045,16 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="H163" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="I163" t="n">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="J163" t="n">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -9014,7 +9070,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9024,7 +9080,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Conventional DL</t>
+          <t>Hex-bar DL</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9038,16 +9094,16 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="H164" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="I164" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J164" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -9063,17 +9119,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>upper_strength</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Conventional DL</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9087,16 +9143,16 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="H165" t="n">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="I165" t="n">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="J165" t="n">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -9112,22 +9168,22 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>upper_strength</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Pull-ups (no time)</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9136,16 +9192,16 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="H166" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="I166" t="n">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="J166" t="n">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -9161,7 +9217,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9171,7 +9227,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Push-ups (2 min)</t>
+          <t>Pull-ups (no time)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9185,16 +9241,16 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="H167" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="I167" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="J167" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -9210,17 +9266,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>core_endurance</t>
+          <t>upper_endurance</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Sit-ups (2 min)</t>
+          <t>Push-ups (2 min)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -9237,13 +9293,13 @@
         <v>50</v>
       </c>
       <c r="H168" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I168" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J168" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -9259,22 +9315,22 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>stability</t>
+          <t>core_endurance</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Plank (front)</t>
+          <t>Sit-ups (2 min)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>reps</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -9282,25 +9338,17 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>1:30</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>2:30</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>3:30</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>4:30</t>
-        </is>
+      <c r="G169" t="n">
+        <v>50</v>
+      </c>
+      <c r="H169" t="n">
+        <v>75</v>
+      </c>
+      <c r="I169" t="n">
+        <v>90</v>
+      </c>
+      <c r="J169" t="n">
+        <v>110</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -9316,7 +9364,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9326,7 +9374,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Side plank (per side)</t>
+          <t>Plank (front)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -9341,22 +9389,22 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>1:00</t>
+          <t>1:30</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>1:30</t>
+          <t>2:30</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2:00</t>
+          <t>3:30</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>3:00</t>
+          <t>4:30</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9373,17 +9421,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>UK Infantry</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>grip</t>
+          <t>stability</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Dead hang (grip)</t>
+          <t>Side plank (per side)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -9398,22 +9446,22 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>0:35</t>
+          <t>1:00</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>1:00</t>
+          <t>1:30</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1:30</t>
+          <t>2:00</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2:00</t>
+          <t>3:00</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -9430,22 +9478,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>UK Police JRFT</t>
+          <t>UK Special Forces (SAS/SBS)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>grip</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Multi-stage bleep test</t>
+          <t>Dead hang (grip)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9453,26 +9501,29 @@
           <t>higher-is-better</t>
         </is>
       </c>
-      <c r="G172" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H172" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I172" t="n">
-        <v>10</v>
-      </c>
-      <c r="J172" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>elite</t>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>0:45</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>1:15</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>2:30</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
     </row>
@@ -9484,49 +9535,52 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>UK Police JRFT</t>
+          <t>UK Infantry</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>upper_strength</t>
+          <t>running</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Pull (dynamometer)</t>
+          <t>2 km run (best effort)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G173" t="n">
-        <v>35</v>
-      </c>
-      <c r="H173" t="n">
-        <v>45</v>
-      </c>
-      <c r="I173" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="J173" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>good+excellent+elite</t>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>8:45</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>7:45</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>7:15</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
     </row>
@@ -9538,49 +9592,52 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>UK Police JRFT</t>
+          <t>UK Infantry</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>upper_strength</t>
+          <t>rucking</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Push (dynamometer)</t>
+          <t>8-mile loaded march (25 kg)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G174" t="n">
-        <v>34</v>
-      </c>
-      <c r="H174" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="I174" t="n">
-        <v>50</v>
-      </c>
-      <c r="J174" t="n">
-        <v>60</v>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>good+excellent+elite</t>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2:00:00</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>1:55:00</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1:50:00</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>1:40:00</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
     </row>
@@ -9592,22 +9649,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>UK ARU / SCO19</t>
+          <t>UK Infantry</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Bleep test (with armour vest ~7 kg)</t>
+          <t>Back Squat</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9616,25 +9673,20 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>7.6</v>
+        <v>100</v>
       </c>
       <c r="H175" t="n">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="I175" t="n">
-        <v>10.5</v>
+        <v>155</v>
       </c>
       <c r="J175" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>elite</t>
-        </is>
+        <v>175</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
     </row>
@@ -9646,57 +9698,44 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>UK ARU / SCO19</t>
+          <t>UK Infantry</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Vested 1-mile run (~7 kg)</t>
+          <t>Hex-bar DL</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>min:sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>lower-is-better</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>9:00</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>7:30</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>6:00</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>4:30</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>excellent+elite</t>
-        </is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>120</v>
+      </c>
+      <c r="H176" t="n">
+        <v>155</v>
+      </c>
+      <c r="I176" t="n">
+        <v>185</v>
+      </c>
+      <c r="J176" t="n">
+        <v>210</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
     </row>
@@ -9708,57 +9747,44 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>UK ARU / SCO19</t>
+          <t>UK Infantry</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>lower_strength</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Casualty drag (75 kg dummy, 15 m)</t>
+          <t>Conventional DL</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>lower-is-better</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>0:00:30</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>0:00:20</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>0:00:12</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>0:00:08</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>excellent+elite</t>
-        </is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>110</v>
+      </c>
+      <c r="H177" t="n">
+        <v>140</v>
+      </c>
+      <c r="I177" t="n">
+        <v>170</v>
+      </c>
+      <c r="J177" t="n">
+        <v>195</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
     </row>
@@ -9770,22 +9796,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>UK ARU / SCO19</t>
+          <t>UK Infantry</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>upper_endurance</t>
+          <t>upper_strength</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Pull-ups</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>reps</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9794,25 +9820,20 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="H178" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="I178" t="n">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="J178" t="n">
-        <v>18</v>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>excellent+elite</t>
-        </is>
+        <v>135</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>ORS</t>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
     </row>
@@ -9824,47 +9845,759 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
+          <t>UK Infantry</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>upper_endurance</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Pull-ups (no time)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>reps</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>6</v>
+      </c>
+      <c r="H179" t="n">
+        <v>12</v>
+      </c>
+      <c r="I179" t="n">
+        <v>18</v>
+      </c>
+      <c r="J179" t="n">
+        <v>25</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>UK Infantry</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>upper_endurance</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Push-ups (2 min)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>reps</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>45</v>
+      </c>
+      <c r="H180" t="n">
+        <v>65</v>
+      </c>
+      <c r="I180" t="n">
+        <v>80</v>
+      </c>
+      <c r="J180" t="n">
+        <v>100</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>UK Infantry</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>core_endurance</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Sit-ups (2 min)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>reps</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>50</v>
+      </c>
+      <c r="H181" t="n">
+        <v>70</v>
+      </c>
+      <c r="I181" t="n">
+        <v>90</v>
+      </c>
+      <c r="J181" t="n">
+        <v>110</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>UK Infantry</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Plank (front)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>sec</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2:30</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>3:30</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>4:30</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>UK Infantry</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>stability</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Side plank (per side)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>sec</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>1:00</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>2:00</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>3:00</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>UK Infantry</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>grip</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Dead hang (grip)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>sec</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>0:35</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>1:00</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>1:30</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2:00</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>ORS (tpf-app mirror 2026-07-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>UK Police JRFT</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Multi-stage bleep test</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H185" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I185" t="n">
+        <v>10</v>
+      </c>
+      <c r="J185" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>UK Police JRFT</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>upper_strength</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Pull (dynamometer)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>35</v>
+      </c>
+      <c r="H186" t="n">
+        <v>45</v>
+      </c>
+      <c r="I186" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="J186" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>good+excellent+elite</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>UK Police JRFT</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>upper_strength</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Push (dynamometer)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>34</v>
+      </c>
+      <c r="H187" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="I187" t="n">
+        <v>50</v>
+      </c>
+      <c r="J187" t="n">
+        <v>60</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>good+excellent+elite</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
           <t>UK ARU / SCO19</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Bleep test (with armour vest ~7 kg)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H188" t="n">
+        <v>9</v>
+      </c>
+      <c r="I188" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J188" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>UK ARU / SCO19</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Vested 1-mile run (~7 kg)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>min:sec</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>9:00</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>7:30</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>6:00</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>4:30</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>excellent+elite</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>UK ARU / SCO19</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Casualty drag (75 kg dummy, 15 m)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>sec</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>lower-is-better</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>0:00:30</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>0:00:20</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>0:00:12</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>0:00:08</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>excellent+elite</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>UK ARU / SCO19</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
         <is>
           <t>upper_endurance</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Pull-ups</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>reps</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>6</v>
+      </c>
+      <c r="H191" t="n">
+        <v>10</v>
+      </c>
+      <c r="I191" t="n">
+        <v>14</v>
+      </c>
+      <c r="J191" t="n">
+        <v>18</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>excellent+elite</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>UK ARU / SCO19</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>upper_endurance</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
         <is>
           <t>Push-ups (1 min)</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>reps</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>higher-is-better</t>
-        </is>
-      </c>
-      <c r="G179" t="n">
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>higher-is-better</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
         <v>30</v>
       </c>
-      <c r="H179" t="n">
+      <c r="H192" t="n">
         <v>50</v>
       </c>
-      <c r="I179" t="n">
+      <c r="I192" t="n">
         <v>70</v>
       </c>
-      <c r="J179" t="n">
+      <c r="J192" t="n">
         <v>90</v>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="K192" t="inlineStr">
         <is>
           <t>excellent+elite</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t>ORS</t>
         </is>
@@ -9881,7 +10614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10626,6 +11359,51 @@
         <v>100</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>US Navy (PRT)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/config/standards/TPF_Operator_Standards.xlsx
+++ b/config/standards/TPF_Operator_Standards.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,10 +539,34 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>2026-10-02, later (Navy PRT + the minimum / good / maximum rule, tpf-app mirror): a ladder read off a general military table puts the official maximum at Excellent at most, with Elite above it (TPF's margin: +10 % reps / hold, -5 % time) — USMC and US Police PFT Elites moved; SEAL pull-up Pass raised to the PST minimum (10). New unit 'US Navy (PRT)' on the Navy PRT Guide-5 (Jan 2025) table, men 17-19. Two new columns: 'id' (overrides the id codegen makes from the name; blank = as before) and 'alternative_group' (benchmarks sharing one score once, at the best — the Navy cardio event). Record: scripts/apply-navy-prt-and-military-tiers-2026-10-02.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-02, latest (military top tiers, tpf-app mirror; record: tpf-app docs/build/54_MILITARY_TOP_TIERS_COMPARISON.md section 11): the top tier of a general military ladder is now the HARDER of a comparison ladder's elite point and the table maximum + TPF's margin — USMC push-ups (2 min) Elite 96 -&gt; 100, USMC plank 4:10 -&gt; 4:30, Navy PRT forearm plank 3:45 -&gt; 4:30. And, the owner: an Elite deadlift is always over 200 kg — every unit's conventional and hex-bar deadlift Elite moved to 205-255 kg by TPF's method (order between units kept; hex at least 1.06 x conventional); Pass, Good and Excellent unchanged. Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-03 (special-forces and elite-unit tiers, tpf-app mirror; record: tpf-app docs/build/55_SPECIAL_FORCES_AND_ELITE_UNIT_TIERS.md section 10.2): a special-forces top is the harder of the general Elite and the hardest general unit's top — SEAL, Pararescue, SFAS and UKSF squat / bench / pull-ups / push-ups / sit-ups Elites raised (squat 190, bench 160, pull-ups 25, push-ups 105, sit-ups 110), UKSF deadlift Elites 225 / 245, Pararescue hex 245. Runs: SEAL / Pararescue 1.5-mile Elite 8:15, SFAS 2-mile 11:15, Para Reg 2 km 6:20, US Airborne 2-mile Excellent 12:30 / Elite 11:45. UKSF 5-mile @ 30 kg Elite 55:00. The Fan Dance names the selection load (18 kg bergen + rifle + water) and Pass moved to the published 4:10:00. The SEAL run and swim and the Pararescue swim name their conditions (the owner: 'label conditions'); renamed rows keep their ids (the `id` column). Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-03, later (the deadlift Excellent evened out, tpf-app mirror; record: tpf-app docs/build/55_SPECIAL_FORCES_AND_ELITE_UNIT_TIERS.md section 10.1): the owner, shown police at 90 / 115 / 140 / 205 kg, 'Even it out a bit 170kg is barely elite'. On every unit and both bars, Excellent = (Good + Elite) / 2 rounded to the nearest 5 kg (a half rounds up), only ever raised — all 25 deadlift rows here rose; Pass, Good and Elite unchanged. Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
         </is>
       </c>
     </row>
@@ -783,14 +807,14 @@
         <v>150</v>
       </c>
       <c r="I5" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="J5" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 230 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 175 -&gt; 190 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -832,14 +856,14 @@
         <v>135</v>
       </c>
       <c r="I6" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J6" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 180 -&gt; 215 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 160 -&gt; 175 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -982,11 +1006,11 @@
         <v>75</v>
       </c>
       <c r="J9" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 87 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 87 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02; Elite 96 -&gt; 100: the harder of the special-forces median top rung (100) and the PFT maximum + margin (96) — tpf-app mirror 2026-10-02 (plan 54 §11)</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1062,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4:10</t>
+          <t>4:30</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 3:45 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 3:45 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02; Elite 4:10 -&gt; 4:30: the harder of the app's operator plank Elite (4:30) and the PFT maximum + margin (4:10) — tpf-app mirror 2026-10-02 (plan 54 §11)</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1326,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Excellent 13:30 -&gt; 12:30 and Elite 12:30 -&gt; 11:45: the general rule for runs — the AFT Benchmarks test's 'Elite' rung and Tier 1 (plan 55 Q3) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -1460,14 +1484,14 @@
         <v>145</v>
       </c>
       <c r="I18" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J18" t="n">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 205 -&gt; 240 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 185 -&gt; 195 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -1509,14 +1533,14 @@
         <v>140</v>
       </c>
       <c r="I19" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J19" t="n">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 185 -&gt; 220 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 165 -&gt; 180 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2383,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 12:00 -&gt; 11:15: a special-forces run top is at least the general Advanced and the fastest published maximum (plan 55 R1; the owner, 2026-10-02: 'if recommended are 1.5 mile fine') — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -2569,14 +2593,14 @@
         <v>180</v>
       </c>
       <c r="I39" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="J39" t="n">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 235 -&gt; 255 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 210 -&gt; 220 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -2618,14 +2642,14 @@
         <v>165</v>
       </c>
       <c r="I40" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J40" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 215 -&gt; 230 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 195 -&gt; 200 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -2670,11 +2694,11 @@
         <v>130</v>
       </c>
       <c r="J41" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 155 -&gt; 160: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -2817,11 +2841,11 @@
         <v>80</v>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -2866,11 +2890,11 @@
         <v>90</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 110: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3185,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.5-mile run</t>
+          <t>1.5-mile run (PST: in boots and trousers)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3191,12 +3215,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8:30</t>
+          <t>8:15</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 8:30 -&gt; 8:15: a special-forces run top is at least the general Advanced and the fastest published maximum (plan 55 R1; the owner, 2026-10-02: 'if recommended are 1.5 mile fine') — tpf-app mirror 2026-10-03 (plan 55 §10.2); Renamed '1.5-mile run' -&gt; '1.5-mile run (PST: in boots and trousers)', the app's label, which states the test's conditions (the owner, 2026-10-02: 'label conditions'); no number converted; id pinned to '1_5_mile_run' so stored results and the app sync still match — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1_5_mile_run</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3247,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>500 m swim</t>
+          <t>500 m swim (PST: 500 yd sidestroke or breaststroke, converted)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3253,7 +3282,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BUD/S PST 500-yd swim x 1.0995 (Riegel 1.06) to 500 m — tpf-app mirror 2026-10-02</t>
+          <t>BUD/S PST 500-yd swim x 1.0995 (Riegel 1.06) to 500 m — tpf-app mirror 2026-10-02; Renamed '500 m swim' -&gt; '500 m swim (PST: 500 yd sidestroke or breaststroke, converted)', the app's label, which states the test's conditions (the owner, 2026-10-02: 'label conditions'); no number converted; id pinned to '500_m_swim' so stored results and the app sync still match — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>500_m_swim</t>
         </is>
       </c>
     </row>
@@ -3298,11 +3332,11 @@
         <v>150</v>
       </c>
       <c r="J53" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 180 -&gt; 190: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3344,14 +3378,14 @@
         <v>160</v>
       </c>
       <c r="I54" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="J54" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 215 -&gt; 250 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 190 -&gt; 205 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -3393,14 +3427,14 @@
         <v>145</v>
       </c>
       <c r="I55" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="J55" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 175 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -3445,11 +3479,11 @@
         <v>120</v>
       </c>
       <c r="J56" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 140 -&gt; 160: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3494,11 +3528,11 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Pass = the BUD/S PST minimum of 10 (was 8, below it) — tpf-app mirror 2026-10-02</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Pass = the BUD/S PST minimum of 10 (was 8, below it) — tpf-app mirror 2026-10-02; Elite 22 -&gt; 25: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3543,11 +3577,11 @@
         <v>80</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3951,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8:30</t>
+          <t>8:15</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 8:30 -&gt; 8:15: a special-forces run top is at least the general Advanced and the fastest published maximum (plan 55 R1; the owner, 2026-10-02: 'if recommended are 1.5 mile fine') — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4035,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>500 m swim</t>
+          <t>500 m swim (PAST: freestyle, breaststroke or sidestroke)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4036,7 +4070,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Renamed '500 m swim' -&gt; '500 m swim (PAST: freestyle, breaststroke or sidestroke)', the app's label, which states the test's conditions (the owner, 2026-10-02: 'label conditions'); no number converted; id pinned to '500_m_swim' so stored results and the app sync still match — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>500_m_swim</t>
         </is>
       </c>
     </row>
@@ -4081,11 +4120,11 @@
         <v>145</v>
       </c>
       <c r="J68" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 175 -&gt; 190: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4127,14 +4166,14 @@
         <v>140</v>
       </c>
       <c r="I69" t="n">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="J69" t="n">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 230 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Elite 230 -&gt; 245: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2); Excellent 170 -&gt; 195 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -4179,11 +4218,11 @@
         <v>115</v>
       </c>
       <c r="J70" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 135 -&gt; 160: consistency with the other special-forces tops (plan 55 §4.1); weight 0 here and in the app, so no score effect — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4228,11 +4267,11 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 22 -&gt; 25: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4277,11 +4316,11 @@
         <v>85</v>
       </c>
       <c r="J72" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4326,11 +4365,11 @@
         <v>90</v>
       </c>
       <c r="J73" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 110: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4546,11 +4585,11 @@
         <v>95</v>
       </c>
       <c r="J77" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 110 -&gt; 120: consistency with the other special-forces tops (plan 55 §4.1); weight 0 here and in the app, so no score effect — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4804,14 +4843,14 @@
         <v>155</v>
       </c>
       <c r="I82" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J82" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 210 -&gt; 245 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 185 -&gt; 200 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -4853,14 +4892,14 @@
         <v>140</v>
       </c>
       <c r="I83" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J83" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 170 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -5571,14 +5610,14 @@
         <v>130</v>
       </c>
       <c r="I96" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="J96" t="n">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02; Elite 185 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 160 -&gt; 180 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -5620,14 +5659,14 @@
         <v>115</v>
       </c>
       <c r="I97" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="J97" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02; Elite 170 -&gt; 210 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 145 -&gt; 165 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -5777,12 +5816,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>3:45</t>
+          <t>4:30</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02; Elite 3:45 -&gt; 4:30: the harder of the app's operator plank Elite (4:30) and Outstanding High + margin (3:45); Excellent kept at Excellent High 3:04 (plan 54 F5) — tpf-app mirror 2026-10-02 (plan 54 §11)</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6090,14 +6129,14 @@
         <v>125</v>
       </c>
       <c r="I106" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="J106" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 170 -&gt; 220 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 150 -&gt; 175 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -6139,14 +6178,14 @@
         <v>115</v>
       </c>
       <c r="I107" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="J107" t="n">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 160 -&gt; 205 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 140 -&gt; 160 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -6759,14 +6798,14 @@
         <v>160</v>
       </c>
       <c r="I119" t="n">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="J119" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 210 -&gt; 245 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 185 -&gt; 205 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -6808,14 +6847,14 @@
         <v>145</v>
       </c>
       <c r="I120" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J120" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 170 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7420,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>6:45</t>
+          <t>6:20</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 6:45 -&gt; 6:20: the paras may be the fastest runners (the owner, 2026-10-02: 'paras only', plan 55 Q3) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -7534,14 +7573,14 @@
         <v>140</v>
       </c>
       <c r="I134" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J134" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 200 -&gt; 235 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 180 -&gt; 190 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -7583,14 +7622,14 @@
         <v>135</v>
       </c>
       <c r="I135" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J135" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 180 -&gt; 215 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 160 -&gt; 175 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -8317,14 +8356,14 @@
         <v>160</v>
       </c>
       <c r="I149" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="J149" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 215 -&gt; 250 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 190 -&gt; 205 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -8366,14 +8405,14 @@
         <v>145</v>
       </c>
       <c r="I150" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="J150" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 175 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8986,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>1:00:00</t>
+          <t>55:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 1:00:00 -&gt; 55:00: special-forces ruck tops lead every general unit's (plan 55 Q1, option B); the app's cite: 'UK SF 5-mile @ 30 kg — 15 min/mile pass; 11 min/mile elite (TPF, plan 55)' — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -8974,7 +9013,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Fan Dance (24 km @ 35 lb + rifle) — optional</t>
+          <t>Fan Dance (24 km, 18 kg bergen + rifle + water) — optional</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8989,7 +9028,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>4:00:00</t>
+          <t>4:10:00</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -9009,7 +9048,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); The selection load and its published cut-off (the owner, 2026-10-02: 'Fan dance should be with proper weight'): renamed from 'Fan Dance (24 km @ 35 lb + rifle) — optional'; Pass 4:00:00 -&gt; 4:10:00; Good, Excellent and Elite kept; the app's cite: 'UKSF selection Fan Dance: 4 h 10 min allowed; 18 kg bergen + rifle + water (third-party accounts)' (plan 55 §10.3); id pinned to 'fan_dance_24_km_35_lb_rifle_optional' so stored results still match — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>fan_dance_24_km_35_lb_rifle_optional</t>
         </is>
       </c>
     </row>
@@ -9054,11 +9098,11 @@
         <v>140</v>
       </c>
       <c r="J163" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 165 -&gt; 190: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -9100,14 +9144,14 @@
         <v>160</v>
       </c>
       <c r="I164" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J164" t="n">
-        <v>200</v>
+        <v>245</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 200 -&gt; 235 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Elite 235 -&gt; 245: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2); Excellent 175 -&gt; 205 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -9149,14 +9193,14 @@
         <v>145</v>
       </c>
       <c r="I165" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="J165" t="n">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 185 -&gt; 220 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Elite 220 -&gt; 225: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2); Excellent 165 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -9201,11 +9245,11 @@
         <v>110</v>
       </c>
       <c r="J166" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 140 -&gt; 160: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -9250,11 +9294,11 @@
         <v>18</v>
       </c>
       <c r="J167" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 22 -&gt; 25: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -9299,11 +9343,11 @@
         <v>80</v>
       </c>
       <c r="J168" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -9728,14 +9772,14 @@
         <v>155</v>
       </c>
       <c r="I176" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J176" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 210 -&gt; 245 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 185 -&gt; 200 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -9777,14 +9821,14 @@
         <v>140</v>
       </c>
       <c r="I177" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J177" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 170 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>

--- a/config/standards/TPF_Operator_Standards.xlsx
+++ b/config/standards/TPF_Operator_Standards.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,10 +563,18 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>2026-10-03, later (the deadlift Excellent evened out, tpf-app mirror; record: tpf-app docs/build/55_SPECIAL_FORCES_AND_ELITE_UNIT_TIERS.md section 10.1): the owner, shown police at 90 / 115 / 140 / 205 kg, 'Even it out a bit 170kg is barely elite'. On every unit and both bars, Excellent = (Good + Elite) / 2 rounded to the nearest 5 kg (a half rounds up), only ever raised — all 25 deadlift rows here rose; Pass, Good and Elite unchanged. Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-03, latest (the Fan Dance's faster tiers, tpf-app mirror; record: tpf-app docs/build/55_SPECIAL_FORCES_AND_ELITE_UNIT_TIERS.md section 11.1): told the kept 3:00 Elite at the ~23 kg selection load is close to unreachable, the owner: 'adjust times then'. UKSF Fan Dance Good 3:30:00 -&gt; 3:55:00, Excellent 3:15:00 -&gt; 3:40:00, Elite 3:00:00 -&gt; 3:30:00; Pass stays the published 4:10:00. TPF's method (the app's ruck model plus its hilly-terrain band for the ~1,100 m climb), not a source. Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
         </is>
       </c>
     </row>
@@ -9033,22 +9041,22 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
+          <t>3:55:00</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>3:40:00</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
           <t>3:30:00</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>3:15:00</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>3:00:00</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); The selection load and its published cut-off (the owner, 2026-10-02: 'Fan dance should be with proper weight'): renamed from 'Fan Dance (24 km @ 35 lb + rifle) — optional'; Pass 4:00:00 -&gt; 4:10:00; Good, Excellent and Elite kept; the app's cite: 'UKSF selection Fan Dance: 4 h 10 min allowed; 18 kg bergen + rifle + water (third-party accounts)' (plan 55 §10.3); id pinned to 'fan_dance_24_km_35_lb_rifle_optional' so stored results still match — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); The selection load and its published cut-off (the owner, 2026-10-02: 'Fan dance should be with proper weight'): renamed from 'Fan Dance (24 km @ 35 lb + rifle) — optional'; Pass 4:00:00 -&gt; 4:10:00; Good, Excellent and Elite kept; the app's cite: 'UKSF selection Fan Dance: 4 h 10 min allowed; 18 kg bergen + rifle + water (third-party accounts)' (plan 55 §10.3); id pinned to 'fan_dance_24_km_35_lb_rifle_optional' so stored results still match — tpf-app mirror 2026-10-03 (plan 55 §10.2); Good 3:30:00 -&gt; 3:55:00, Excellent 3:15:00 -&gt; 3:40:00, Elite 3:00:00 -&gt; 3:30:00; Pass kept at the published 4:10:00 (the owner, 2026-10-03, told a 3:00 Elite at the ~23 kg selection load is close to unreachable: 'adjust times then'). TPF's method, not a source: the app's ruck model plus its hilly-terrain band (x 1.15) for the ~1,100 m of ascent; Elite 3:30 reads 2:16:38 on the app's 12 mi @ 35 lb scale (inside the special-forces band, between Pararescue and the Rangers) and is slower than the best known 35 lb time (3:14, third-party) carried to 23 kg; Good and Excellent split the 40 minutes 20 : 15 : 15 like the tier percentages, to the nearest 5 min. Label unchanged; the app's cite now reads: 'UKSF selection Fan Dance: 4 h 10 min allowed; 18 kg bergen + rifle + water (third-party accounts). Faster tiers TPF's: the ruck model plus a hilly-terrain climb allowance (plan 55 §11)' — tpf-app mirror 2026-10-03 (plan 55 §11.1)</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">

--- a/config/standards/TPF_Operator_Standards.xlsx
+++ b/config/standards/TPF_Operator_Standards.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,10 +539,42 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>2026-10-02, later (Navy PRT + the minimum / good / maximum rule, tpf-app mirror): a ladder read off a general military table puts the official maximum at Excellent at most, with Elite above it (TPF's margin: +10 % reps / hold, -5 % time) — USMC and US Police PFT Elites moved; SEAL pull-up Pass raised to the PST minimum (10). New unit 'US Navy (PRT)' on the Navy PRT Guide-5 (Jan 2025) table, men 17-19. Two new columns: 'id' (overrides the id codegen makes from the name; blank = as before) and 'alternative_group' (benchmarks sharing one score once, at the best — the Navy cardio event). Record: scripts/apply-navy-prt-and-military-tiers-2026-10-02.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-02, latest (military top tiers, tpf-app mirror; record: tpf-app docs/build/54_MILITARY_TOP_TIERS_COMPARISON.md section 11): the top tier of a general military ladder is now the HARDER of a comparison ladder's elite point and the table maximum + TPF's margin — USMC push-ups (2 min) Elite 96 -&gt; 100, USMC plank 4:10 -&gt; 4:30, Navy PRT forearm plank 3:45 -&gt; 4:30. And, the owner: an Elite deadlift is always over 200 kg — every unit's conventional and hex-bar deadlift Elite moved to 205-255 kg by TPF's method (order between units kept; hex at least 1.06 x conventional); Pass, Good and Excellent unchanged. Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-03 (special-forces and elite-unit tiers, tpf-app mirror; record: tpf-app docs/build/55_SPECIAL_FORCES_AND_ELITE_UNIT_TIERS.md section 10.2): a special-forces top is the harder of the general Elite and the hardest general unit's top — SEAL, Pararescue, SFAS and UKSF squat / bench / pull-ups / push-ups / sit-ups Elites raised (squat 190, bench 160, pull-ups 25, push-ups 105, sit-ups 110), UKSF deadlift Elites 225 / 245, Pararescue hex 245. Runs: SEAL / Pararescue 1.5-mile Elite 8:15, SFAS 2-mile 11:15, Para Reg 2 km 6:20, US Airborne 2-mile Excellent 12:30 / Elite 11:45. UKSF 5-mile @ 30 kg Elite 55:00. The Fan Dance names the selection load (18 kg bergen + rifle + water) and Pass moved to the published 4:10:00. The SEAL run and swim and the Pararescue swim name their conditions (the owner: 'label conditions'); renamed rows keep their ids (the `id` column). Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-03, later (the deadlift Excellent evened out, tpf-app mirror; record: tpf-app docs/build/55_SPECIAL_FORCES_AND_ELITE_UNIT_TIERS.md section 10.1): the owner, shown police at 90 / 115 / 140 / 205 kg, 'Even it out a bit 170kg is barely elite'. On every unit and both bars, Excellent = (Good + Elite) / 2 rounded to the nearest 5 kg (a half rounds up), only ever raised — all 25 deadlift rows here rose; Pass, Good and Elite unchanged. Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-03, latest (the Fan Dance's faster tiers, tpf-app mirror; record: tpf-app docs/build/55_SPECIAL_FORCES_AND_ELITE_UNIT_TIERS.md section 11.1): told the kept 3:00 Elite at the ~23 kg selection load is close to unreachable, the owner: 'adjust times then'. UKSF Fan Dance Good 3:30:00 -&gt; 3:55:00, Excellent 3:15:00 -&gt; 3:40:00, Elite 3:00:00 -&gt; 3:30:00; Pass stays the published 4:10:00. TPF's method (the app's ruck model plus its hilly-terrain band for the ~1,100 m climb), not a source. Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
         </is>
       </c>
     </row>
@@ -783,14 +815,14 @@
         <v>150</v>
       </c>
       <c r="I5" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="J5" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 230 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 175 -&gt; 190 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -832,14 +864,14 @@
         <v>135</v>
       </c>
       <c r="I6" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J6" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 180 -&gt; 215 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 160 -&gt; 175 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -982,11 +1014,11 @@
         <v>75</v>
       </c>
       <c r="J9" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 87 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 87 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02; Elite 96 -&gt; 100: the harder of the special-forces median top rung (100) and the PFT maximum + margin (96) — tpf-app mirror 2026-10-02 (plan 54 §11)</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1070,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4:10</t>
+          <t>4:30</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 3:45 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 3:45 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02; Elite 4:10 -&gt; 4:30: the harder of the app's operator plank Elite (4:30) and the PFT maximum + margin (4:10) — tpf-app mirror 2026-10-02 (plan 54 §11)</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1334,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Excellent 13:30 -&gt; 12:30 and Elite 12:30 -&gt; 11:45: the general rule for runs — the AFT Benchmarks test's 'Elite' rung and Tier 1 (plan 55 Q3) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -1460,14 +1492,14 @@
         <v>145</v>
       </c>
       <c r="I18" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J18" t="n">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 205 -&gt; 240 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 185 -&gt; 195 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -1509,14 +1541,14 @@
         <v>140</v>
       </c>
       <c r="I19" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J19" t="n">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 185 -&gt; 220 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 165 -&gt; 180 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -2359,12 +2391,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 12:00 -&gt; 11:15: a special-forces run top is at least the general Advanced and the fastest published maximum (plan 55 R1; the owner, 2026-10-02: 'if recommended are 1.5 mile fine') — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -2569,14 +2601,14 @@
         <v>180</v>
       </c>
       <c r="I39" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="J39" t="n">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 235 -&gt; 255 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 210 -&gt; 220 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -2618,14 +2650,14 @@
         <v>165</v>
       </c>
       <c r="I40" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J40" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 215 -&gt; 230 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 195 -&gt; 200 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -2670,11 +2702,11 @@
         <v>130</v>
       </c>
       <c r="J41" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 155 -&gt; 160: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -2817,11 +2849,11 @@
         <v>80</v>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -2866,11 +2898,11 @@
         <v>90</v>
       </c>
       <c r="J45" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 110: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3193,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.5-mile run</t>
+          <t>1.5-mile run (PST: in boots and trousers)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3191,12 +3223,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>8:30</t>
+          <t>8:15</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 8:30 -&gt; 8:15: a special-forces run top is at least the general Advanced and the fastest published maximum (plan 55 R1; the owner, 2026-10-02: 'if recommended are 1.5 mile fine') — tpf-app mirror 2026-10-03 (plan 55 §10.2); Renamed '1.5-mile run' -&gt; '1.5-mile run (PST: in boots and trousers)', the app's label, which states the test's conditions (the owner, 2026-10-02: 'label conditions'); no number converted; id pinned to '1_5_mile_run' so stored results and the app sync still match — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1_5_mile_run</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3255,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>500 m swim</t>
+          <t>500 m swim (PST: 500 yd sidestroke or breaststroke, converted)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3253,7 +3290,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BUD/S PST 500-yd swim x 1.0995 (Riegel 1.06) to 500 m — tpf-app mirror 2026-10-02</t>
+          <t>BUD/S PST 500-yd swim x 1.0995 (Riegel 1.06) to 500 m — tpf-app mirror 2026-10-02; Renamed '500 m swim' -&gt; '500 m swim (PST: 500 yd sidestroke or breaststroke, converted)', the app's label, which states the test's conditions (the owner, 2026-10-02: 'label conditions'); no number converted; id pinned to '500_m_swim' so stored results and the app sync still match — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>500_m_swim</t>
         </is>
       </c>
     </row>
@@ -3298,11 +3340,11 @@
         <v>150</v>
       </c>
       <c r="J53" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 180 -&gt; 190: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3344,14 +3386,14 @@
         <v>160</v>
       </c>
       <c r="I54" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="J54" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 215 -&gt; 250 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 190 -&gt; 205 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -3393,14 +3435,14 @@
         <v>145</v>
       </c>
       <c r="I55" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="J55" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 175 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -3445,11 +3487,11 @@
         <v>120</v>
       </c>
       <c r="J56" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 140 -&gt; 160: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3494,11 +3536,11 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Pass = the BUD/S PST minimum of 10 (was 8, below it) — tpf-app mirror 2026-10-02</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Pass = the BUD/S PST minimum of 10 (was 8, below it) — tpf-app mirror 2026-10-02; Elite 22 -&gt; 25: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3543,11 +3585,11 @@
         <v>80</v>
       </c>
       <c r="J58" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3959,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>8:30</t>
+          <t>8:15</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 8:30 -&gt; 8:15: a special-forces run top is at least the general Advanced and the fastest published maximum (plan 55 R1; the owner, 2026-10-02: 'if recommended are 1.5 mile fine') — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4043,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>500 m swim</t>
+          <t>500 m swim (PAST: freestyle, breaststroke or sidestroke)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4036,7 +4078,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Renamed '500 m swim' -&gt; '500 m swim (PAST: freestyle, breaststroke or sidestroke)', the app's label, which states the test's conditions (the owner, 2026-10-02: 'label conditions'); no number converted; id pinned to '500_m_swim' so stored results and the app sync still match — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>500_m_swim</t>
         </is>
       </c>
     </row>
@@ -4081,11 +4128,11 @@
         <v>145</v>
       </c>
       <c r="J68" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 175 -&gt; 190: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4127,14 +4174,14 @@
         <v>140</v>
       </c>
       <c r="I69" t="n">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="J69" t="n">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 230 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Elite 230 -&gt; 245: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2); Excellent 170 -&gt; 195 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -4179,11 +4226,11 @@
         <v>115</v>
       </c>
       <c r="J70" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 135 -&gt; 160: consistency with the other special-forces tops (plan 55 §4.1); weight 0 here and in the app, so no score effect — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4228,11 +4275,11 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 22 -&gt; 25: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4277,11 +4324,11 @@
         <v>85</v>
       </c>
       <c r="J72" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4326,11 +4373,11 @@
         <v>90</v>
       </c>
       <c r="J73" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 110: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4546,11 +4593,11 @@
         <v>95</v>
       </c>
       <c r="J77" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 110 -&gt; 120: consistency with the other special-forces tops (plan 55 §4.1); weight 0 here and in the app, so no score effect — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -4804,14 +4851,14 @@
         <v>155</v>
       </c>
       <c r="I82" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J82" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 210 -&gt; 245 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 185 -&gt; 200 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -4853,14 +4900,14 @@
         <v>140</v>
       </c>
       <c r="I83" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J83" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 170 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -5571,14 +5618,14 @@
         <v>130</v>
       </c>
       <c r="I96" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="J96" t="n">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02; Elite 185 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 160 -&gt; 180 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -5620,14 +5667,14 @@
         <v>115</v>
       </c>
       <c r="I97" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="J97" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02; Elite 170 -&gt; 210 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 145 -&gt; 165 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -5777,12 +5824,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>3:45</t>
+          <t>4:30</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02</t>
+          <t>US Navy PRT Guide-5 (Jan 2025, a US government work), men 17-19: Probationary / Good High / Excellent High; Elite above Outstanding High (TPF margin: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02; Elite 3:45 -&gt; 4:30: the harder of the app's operator plank Elite (4:30) and Outstanding High + margin (3:45); Excellent kept at Excellent High 3:04 (plan 54 F5) — tpf-app mirror 2026-10-02 (plan 54 §11)</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6090,14 +6137,14 @@
         <v>125</v>
       </c>
       <c r="I106" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="J106" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 170 -&gt; 220 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 150 -&gt; 175 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -6139,14 +6186,14 @@
         <v>115</v>
       </c>
       <c r="I107" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="J107" t="n">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 160 -&gt; 205 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 140 -&gt; 160 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -6759,14 +6806,14 @@
         <v>160</v>
       </c>
       <c r="I119" t="n">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="J119" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 210 -&gt; 245 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 185 -&gt; 205 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -6808,14 +6855,14 @@
         <v>145</v>
       </c>
       <c r="I120" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J120" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 170 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7428,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>6:45</t>
+          <t>6:20</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 6:45 -&gt; 6:20: the paras may be the fastest runners (the owner, 2026-10-02: 'paras only', plan 55 Q3) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -7534,14 +7581,14 @@
         <v>140</v>
       </c>
       <c r="I134" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J134" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 200 -&gt; 235 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 180 -&gt; 190 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -7583,14 +7630,14 @@
         <v>135</v>
       </c>
       <c r="I135" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J135" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 180 -&gt; 215 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 160 -&gt; 175 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -8317,14 +8364,14 @@
         <v>160</v>
       </c>
       <c r="I149" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="J149" t="n">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 215 -&gt; 250 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 190 -&gt; 205 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -8366,14 +8413,14 @@
         <v>145</v>
       </c>
       <c r="I150" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="J150" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 175 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8994,12 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>1:00:00</t>
+          <t>55:00</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 1:00:00 -&gt; 55:00: special-forces ruck tops lead every general unit's (plan 55 Q1, option B); the app's cite: 'UK SF 5-mile @ 30 kg — 15 min/mile pass; 11 min/mile elite (TPF, plan 55)' — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -8974,7 +9021,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Fan Dance (24 km @ 35 lb + rifle) — optional</t>
+          <t>Fan Dance (24 km, 18 kg bergen + rifle + water) — optional</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8989,27 +9036,32 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>4:00:00</t>
+          <t>4:10:00</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
+          <t>3:55:00</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>3:40:00</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
           <t>3:30:00</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>3:15:00</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>3:00:00</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); The selection load and its published cut-off (the owner, 2026-10-02: 'Fan dance should be with proper weight'): renamed from 'Fan Dance (24 km @ 35 lb + rifle) — optional'; Pass 4:00:00 -&gt; 4:10:00; Good, Excellent and Elite kept; the app's cite: 'UKSF selection Fan Dance: 4 h 10 min allowed; 18 kg bergen + rifle + water (third-party accounts)' (plan 55 §10.3); id pinned to 'fan_dance_24_km_35_lb_rifle_optional' so stored results still match — tpf-app mirror 2026-10-03 (plan 55 §10.2); Good 3:30:00 -&gt; 3:55:00, Excellent 3:15:00 -&gt; 3:40:00, Elite 3:00:00 -&gt; 3:30:00; Pass kept at the published 4:10:00 (the owner, 2026-10-03, told a 3:00 Elite at the ~23 kg selection load is close to unreachable: 'adjust times then'). TPF's method, not a source: the app's ruck model plus its hilly-terrain band (x 1.15) for the ~1,100 m of ascent; Elite 3:30 reads 2:16:38 on the app's 12 mi @ 35 lb scale (inside the special-forces band, between Pararescue and the Rangers) and is slower than the best known 35 lb time (3:14, third-party) carried to 23 kg; Good and Excellent split the 40 minutes 20 : 15 : 15 like the tier percentages, to the nearest 5 min. Label unchanged; the app's cite now reads: 'UKSF selection Fan Dance: 4 h 10 min allowed; 18 kg bergen + rifle + water (third-party accounts). Faster tiers TPF's: the ruck model plus a hilly-terrain climb allowance (plan 55 §11)' — tpf-app mirror 2026-10-03 (plan 55 §11.1)</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>fan_dance_24_km_35_lb_rifle_optional</t>
         </is>
       </c>
     </row>
@@ -9054,11 +9106,11 @@
         <v>140</v>
       </c>
       <c r="J163" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 165 -&gt; 190: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -9100,14 +9152,14 @@
         <v>160</v>
       </c>
       <c r="I164" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J164" t="n">
-        <v>200</v>
+        <v>245</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 200 -&gt; 235 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Elite 235 -&gt; 245: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2); Excellent 175 -&gt; 205 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -9149,14 +9201,14 @@
         <v>145</v>
       </c>
       <c r="I165" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="J165" t="n">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 185 -&gt; 220 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Elite 220 -&gt; 225: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2); Excellent 165 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -9201,11 +9253,11 @@
         <v>110</v>
       </c>
       <c r="J166" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 140 -&gt; 160: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -9250,11 +9302,11 @@
         <v>18</v>
       </c>
       <c r="J167" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 22 -&gt; 25: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -9299,11 +9351,11 @@
         <v>80</v>
       </c>
       <c r="J168" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
         </is>
       </c>
     </row>
@@ -9728,14 +9780,14 @@
         <v>155</v>
       </c>
       <c r="I176" t="n">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J176" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 210 -&gt; 245 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 185 -&gt; 200 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>
@@ -9777,14 +9829,14 @@
         <v>140</v>
       </c>
       <c r="I177" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J177" t="n">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 195 -&gt; 225 kg: the owner, 2026-10-02, an Elite deadlift is always over 200 kg; TPF's method (smallest 5 kg value over 200 keeping the order between pathways; hex at least 1.06 x the conventional) — tpf-app mirror 2026-10-02 (plan 54 §11); Excellent 170 -&gt; 185 kg: (Good + Elite) / 2 rounded to the nearest 5 kg, a half rounding up, only ever raised (the owner, 2026-10-03: 'Even it out a bit 170kg is barely elite') — tpf-app mirror 2026-10-03 (plan 55 §10.1)</t>
         </is>
       </c>
     </row>

--- a/config/standards/TPF_Operator_Standards.xlsx
+++ b/config/standards/TPF_Operator_Standards.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,10 +571,18 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>2026-10-03, latest (the Fan Dance's faster tiers, tpf-app mirror; record: tpf-app docs/build/55_SPECIAL_FORCES_AND_ELITE_UNIT_TIERS.md section 11.1): told the kept 3:00 Elite at the ~23 kg selection load is close to unreachable, the owner: 'adjust times then'. UKSF Fan Dance Good 3:30:00 -&gt; 3:55:00, Excellent 3:15:00 -&gt; 3:40:00, Elite 3:00:00 -&gt; 3:30:00; Pass stays the published 4:10:00. TPF's method (the app's ruck model plus its hilly-terrain band for the ~1,100 m climb), not a source. Script: scripts/apply-military-top-tiers-2026-10-02.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-03, last (the missing standards researched — tpf-app plan 61 Part B; record: tpf-app docs/build/61_MISSING_STANDARDS_RESEARCH_2026-10-03.md section 8): USAF Pararescue on the IFT worksheet (10 Jan 2023, PJ column) — 1.5-mile Pass 10:20, 500 m swim Pass 12:30 (civilians enlist on the 15:00 column; the row renamed to the app's label), pull-ups '(2 min)' (renamed, id kept), push-ups Pass 40, sit-ups Pass 50. Broad jump one flat ladder per group: Navy PRT and police 1.70 / 1.95 / 2.20 / 2.40; SEAL, Pararescue and SFAS 1.93 / 2.16 / 2.39 / 2.65 (the AFSPECWAR OFT marks); combat units and SWAT kept. Police plank onto the operator plank 1:30 / 2:30 / 3:30 / 4:30; USMC plank Pass 1:03 -&gt; 1:10. A new `cite` column holds the app's stated basis for every operator-plank, dead-hang and broad-jump row and the Pararescue swim (codegen does not read it; check:app-ors compares it). Script: scripts/apply-standards-research-2026-10-03.py.</t>
         </is>
       </c>
     </row>
@@ -589,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N192"/>
+  <dimension ref="A1:O192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +678,11 @@
           <t>alternative_group</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1055,7 +1068,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1:03</t>
+          <t>1:10</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1075,7 +1088,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 3:45 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02; Elite 4:10 -&gt; 4:30: the harder of the app's operator plank Elite (4:30) and the PFT maximum + margin (4:10) — tpf-app mirror 2026-10-02 (plan 54 §11)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite above the PFT maximum 3:45 (TPF margin above the table maximum: +10 % reps / hold, -5 % time) — tpf-app mirror 2026-10-02; Elite 4:10 -&gt; 4:30: the harder of the app's operator plank Elite (4:30) and the PFT maximum + margin (4:10) — tpf-app mirror 2026-10-02 (plan 54 §11); Pass 1:03 -&gt; 1:10: the USMC PFT plank minimum since 1 Jan 2022 (Marine Corps Times 2021-08-05 and two calculator sites; the order itself returned 403 to the app's research). The app's unit source label now cites MCO 6100.13A (with changes), not 6100.13B, which no source found; this site has no per-unit source label — tpf-app mirror 2026-10-03 (plan 61 §8.2), Part B §9.1-9.2</t>
         </is>
       </c>
     </row>
@@ -1192,6 +1205,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1290,6 +1308,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>TPF's own, checked (plan 61): between the general and special-forces ladders; Elite = the AFSPECWAR OFT maximum (2.39 m)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1804,6 +1827,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1918,6 +1946,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2016,6 +2049,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>TPF's own, checked (plan 61): between the general and special-forces ladders; Elite = the AFSPECWAR OFT maximum (2.39 m)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2962,6 +3000,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3076,6 +3119,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3158,20 +3206,25 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="J50" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Broad jump 1.8 / 2.0 / 2.2 / 2.4 -&gt; 1.93 / 2.16 / 2.39 / 2.65 m: the AFSPECWAR OFT 8 / 9 / 10-point marks (76 / 85 / 94 in, sex-neutral; a US government form, read from a third-party copy, min and max corroborated) and an Elite about the 80th percentile of AFSPECWAR candidates (Feeney 2023, facts) — tpf-app mirror 2026-10-03 (plan 61 §8.2), Part B §3.2</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>AFSPECWAR OFT 8 / 9 / 10-point marks (76 / 85 / 94 in, sex-neutral); Elite 2.65 m ≈ the 80th percentile of AFSPECWAR candidates (plan 61)</t>
         </is>
       </c>
     </row>
@@ -3698,6 +3751,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3812,6 +3870,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3894,20 +3957,25 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="J64" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Broad jump 1.8 / 2.0 / 2.2 / 2.4 -&gt; 1.93 / 2.16 / 2.39 / 2.65 m: the AFSPECWAR OFT 8 / 9 / 10-point marks (76 / 85 / 94 in, sex-neutral; a US government form, read from a third-party copy, min and max corroborated) and an Elite about the 80th percentile of AFSPECWAR candidates (Feeney 2023, facts) — tpf-app mirror 2026-10-03 (plan 61 §8.2), Part B §3.2</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>AFSPECWAR OFT 8 / 9 / 10-point marks (76 / 85 / 94 in, sex-neutral); Elite 2.65 m ≈ the 80th percentile of AFSPECWAR candidates (plan 61)</t>
         </is>
       </c>
     </row>
@@ -3944,7 +4012,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3964,7 +4032,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Elite 8:30 -&gt; 8:15: a special-forces run top is at least the general Advanced and the fastest published maximum (plan 55 R1; the owner, 2026-10-02: 'if recommended are 1.5 mile fine') — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 8:30 -&gt; 8:15: a special-forces run top is at least the general Advanced and the fastest published maximum (plan 55 R1; the owner, 2026-10-02: 'if recommended are 1.5 mile fine') — tpf-app mirror 2026-10-03 (plan 55 §10.2); Pass 10:10 -&gt; 10:20: the USAF IFT worksheet (10 Jan 2023, PJ column — a US government work), the app's 'USAF Pararescue IFT (formerly the PAST)'; the old values were retired PAST numbers (plan 61 Part B §2.3) — tpf-app mirror 2026-10-03 (plan 61 §8.2)</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4111,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>500 m swim (PAST: freestyle, breaststroke or sidestroke)</t>
+          <t>500 m swim (IFT, PJ column — enlistees 15:00; freestyle, breaststroke or sidestroke)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4058,7 +4126,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4078,12 +4146,17 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Renamed '500 m swim' -&gt; '500 m swim (PAST: freestyle, breaststroke or sidestroke)', the app's label, which states the test's conditions (the owner, 2026-10-02: 'label conditions'); no number converted; id pinned to '500_m_swim' so stored results and the app sync still match — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Renamed '500 m swim' -&gt; '500 m swim (PAST: freestyle, breaststroke or sidestroke)', the app's label, which states the test's conditions (the owner, 2026-10-02: 'label conditions'); no number converted; id pinned to '500_m_swim' so stored results and the app sync still match — tpf-app mirror 2026-10-03 (plan 55 §10.2); Pass 12:00 -&gt; 12:30 (the PJ column; civilians enlist on the 9T5 column, 15:00): the USAF IFT worksheet (10 Jan 2023, PJ column — a US government work), the app's 'USAF Pararescue IFT (formerly the PAST)'; the old values were retired PAST numbers (plan 61 Part B §2.3) — tpf-app mirror 2026-10-03 (plan 61 §8.2); Renamed '500 m swim (PAST: freestyle, breaststroke or sidestroke)' -&gt; '500 m swim (IFT, PJ column — enlistees 15:00; freestyle, breaststroke or sidestroke)', the app's label (the IFT's PJ column); id kept '500_m_swim' — tpf-app mirror 2026-10-03 (plan 61 §8.2)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>500_m_swim</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>USAF IFT worksheet (10 Jan 2023), PJ column: 12:30 minimum. Civilians enlist on the 9T5 column, 15:00</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4325,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Pull-ups (no time)</t>
+          <t>Pull-ups (2 min)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4279,7 +4352,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Elite 22 -&gt; 25: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 22 -&gt; 25: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2); Renamed 'Pull-ups (no time)' -&gt; 'Pull-ups (2 min)', the app's label (the IFT allows 2 minutes; 1 minute is for officers); id pinned to 'pull_ups_no_time' so stored results and shared inputs still match — tpf-app mirror 2026-10-03 (plan 61 §8.2)</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>pull_ups_no_time</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4393,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H72" t="n">
         <v>70</v>
@@ -4328,7 +4406,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 105: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2); Pass 50 -&gt; 40: the USAF IFT worksheet (10 Jan 2023, PJ column — a US government work), the app's 'USAF Pararescue IFT (formerly the PAST)'; the old values were retired PAST numbers (plan 61 Part B §2.3) — tpf-app mirror 2026-10-03 (plan 61 §8.2)</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4442,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H73" t="n">
         <v>70</v>
@@ -4377,7 +4455,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 110: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Elite 100 -&gt; 110: a special-forces top is the harder of the general Elite and the hardest general unit's top for the event (the owner, 2026-10-02: 'As you suggest', plan 55 §4.1) — tpf-app mirror 2026-10-03 (plan 55 §10.2); Pass 54 -&gt; 50: the USAF IFT worksheet (10 Jan 2023, PJ column — a US government work), the app's 'USAF Pararescue IFT (formerly the PAST)'; the old values were retired PAST numbers (plan 61 Part B §2.3) — tpf-app mirror 2026-10-03 (plan 61 §8.2)</t>
         </is>
       </c>
     </row>
@@ -4437,6 +4515,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4551,6 +4634,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4633,20 +4721,25 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="J78" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Broad jump 1.8 / 2.0 / 2.2 / 2.4 -&gt; 1.93 / 2.16 / 2.39 / 2.65 m: the AFSPECWAR OFT 8 / 9 / 10-point marks (76 / 85 / 94 in, sex-neutral; a US government form, read from a third-party copy, min and max corroborated) and an Elite about the 80th percentile of AFSPECWAR candidates (Feeney 2023, facts) — tpf-app mirror 2026-10-03 (plan 61 §8.2), Part B §3.2</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>AFSPECWAR OFT 8 / 9 / 10-point marks (76 / 85 / 94 in, sex-neutral); Elite 2.65 m ≈ the 80th percentile of AFSPECWAR candidates (plan 61)</t>
         </is>
       </c>
     </row>
@@ -5163,6 +5256,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5277,6 +5375,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5894,6 +5997,11 @@
           <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5979,17 +6087,22 @@
         <v>1.7</v>
       </c>
       <c r="H103" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02</t>
+          <t>TPF's own (the app's general-military row, shared with its US Army baseline; the PRT has no strength, grip or power event) — tpf-app mirror 2026-10-02; Broad jump 1.7 / 1.9 / 2.1 / 2.3 -&gt; 1.70 / 1.95 / 2.20 / 2.40 m: the general flat ladder (Pass above the US Army OPAT 1.60 m mark; Good / Excellent / Elite at Norwegian conscripts' 25th / 50th / 75th, Aandstad 2023, CC BY; about the AFSPECWAR OFT minimum / 9 points / maximum) — tpf-app mirror 2026-10-03 (plan 61 §8.2), Part B §3.2</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Plan 61: Pass above the OPAT 1.60 m mark; Good / Excellent / Elite ≈ Norwegian conscripts' 25th / 50th / 75th (CC BY) ≈ the AFSPECWAR OFT minimum / 9 pts / maximum</t>
         </is>
       </c>
     </row>
@@ -6426,27 +6539,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1:00</t>
+          <t>1:30</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1:30</t>
+          <t>2:30</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2:30</t>
+          <t>3:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>3:30</t>
+          <t>4:30</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Plank 1:00 / 1:30 / 2:30 / 3:30 -&gt; the operator plank 1:30 / 2:30 / 3:30 / 4:30: the old ladder sat below every US entry-age minimum (USMC / Navy 1:10, AFT 1:20-1:30, PFRA 1:30-1:35); plan 61 Option A — tpf-app mirror 2026-10-03 (plan 61 §8.2), Part B §6.3</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
         </is>
       </c>
     </row>
@@ -6648,17 +6766,22 @@
         <v>1.7</v>
       </c>
       <c r="H116" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J116" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>ORS (tpf-app mirror 2026-07-16)</t>
+          <t>ORS (tpf-app mirror 2026-07-16); Broad jump 1.7 / 1.9 / 2.1 / 2.3 -&gt; 1.70 / 1.95 / 2.20 / 2.40 m: the general flat ladder (Pass above the US Army OPAT 1.60 m mark; Good / Excellent / Elite at Norwegian conscripts' 25th / 50th / 75th, Aandstad 2023, CC BY; about the AFSPECWAR OFT minimum / 9 points / maximum) — tpf-app mirror 2026-10-03 (plan 61 §8.2), Part B §3.2</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Plan 61: Pass above the OPAT 1.60 m mark; Good / Excellent / Elite ≈ Norwegian conscripts' 25th / 50th / 75th (CC BY) ≈ the AFSPECWAR OFT minimum / 9 pts / maximum</t>
         </is>
       </c>
     </row>
@@ -7167,6 +7290,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7281,6 +7409,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7379,6 +7512,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>TPF's own — checked 2026-10-03 (plan 61): Pass ≈ the AFSPECWAR OFT minimum (1.93 m); Elite ≈ the Swiss SOF operator mean + 0.6 SD (CC BY)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7893,6 +8031,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8007,6 +8150,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8105,6 +8253,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>TPF's own, checked (plan 61): between the general and special-forces ladders; Elite = the AFSPECWAR OFT maximum (2.39 m)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8676,6 +8829,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8790,6 +8948,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8888,6 +9051,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>TPF's own, checked (plan 61): between the general and special-forces ladders; Elite = the AFSPECWAR OFT maximum (2.39 m)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9464,6 +9632,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9578,6 +9751,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10092,6 +10270,11 @@
           <t>ORS (tpf-app mirror 2026-07-16)</t>
         </is>
       </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>TPF's operator plank (plan 61): Pass 1:30 = AFT 60 pts = PFRA women's minimum; Good ≈ AFT 78; Excellent ≈ AFT 97; Elite above every US maximum (3:24-3:45)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10204,6 +10387,11 @@
       <c r="L184" t="inlineStr">
         <is>
           <t>ORS (tpf-app mirror 2026-07-16)</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>TPF's own, checked 2026-10-03 (plan 61): no government table uses a dead hang; floors near untrained men's means (40-47 s), tops near elite swimmers' (≈ 95 s). CC BY, men only</t>
         </is>
       </c>
     </row>
